--- a/7.1. Ecommerce - Ventas/Ecommerce.xlsx
+++ b/7.1. Ecommerce - Ventas/Ecommerce.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/abel_matas_dhl_com/Documents/Documents/Copilot/Prompts/Prepare Training/The Valley/Ejercicios/Ecommerce - Ventas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dpdhl-my.sharepoint.com/personal/abel_matas_dhl_com/Documents/Documents/GitHub/TheValley_Manager/7.1. Ecommerce - Ventas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_47B9A1055BB2CEA3E920FD2987FDC89D5B3FD7F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D27E6B64-1C36-407C-8ED6-D8F78094CC1F}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_47B9A1055BB2CEA3E920FD2987FDC89D5B3FD7F4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5A5980F-41E3-4FC9-AFBA-C3CE196BABE7}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-110" windowWidth="29020" windowHeight="15700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -17189,4 +17189,10 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{cd99fef8-1cd3-4a2a-9bdf-15531181d65e}" enabled="0" method="" siteId="{cd99fef8-1cd3-4a2a-9bdf-15531181d65e}" removed="1"/>
+</clbl:labelList>
 </file>